--- a/Configs/GameConfig/Datas/enemystats.xlsx
+++ b/Configs/GameConfig/Datas/enemystats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,84 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mob1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10,11,57,44,39,92,138,200,291,421,611,886,1285,1863,2701,3917,5680,8235,11941,17315</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.6,0.6,0.6,0.6,0.7,0.7,0.7,0.8,0.8,0.8</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mob2</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10,11,57,44,39,92,138,200,291,421,611,886,1285,1863,2701,3917,5680,8235,11941,17315</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.6,0.6,0.6,0.6,0.7,0.7,0.7,0.8,0.8,0.8</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mob3</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10,11,57,44,39,92,138,200,291,421,611,886,1285,1863,2701,3917,5680,8235,11941,17315</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.6,0.6,0.6,0.6,0.7,0.7,0.7,0.8,0.8,0.8</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/enemystats.xlsx
+++ b/Configs/GameConfig/Datas/enemystats.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R058fd1eadb7e4620"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9b24e6a43c4e4a44"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -378,19 +378,19 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>敌人类型键</x:v>
+        <x:v>敌人类型 ID，等于 enemy.Id</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>移动速度(px/s)</x:v>
+        <x:v>移动速度，逻辑像素/秒</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>各波次基础血量(20项)</x:v>
+        <x:v>各难度索引的基础血量列表，wave_plan.difficultyIndex 从 0 开始索引它</x:v>
       </x:c>
       <x:c r="E3" t="str">
-        <x:v>前10波血量乘数</x:v>
+        <x:v>前期波次额外血量倍率</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>接触目标伤害</x:v>
+        <x:v>抵达终点时对目标造成的伤害</x:v>
       </x:c>
       <x:c r="G3" t="str">
         <x:v>击杀奖励金币</x:v>
